--- a/词语表模板.xlsx
+++ b/词语表模板.xlsx
@@ -1,49 +1,426 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s2683227f\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E59A782-D677-485F-A585-C06A63670814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="词语表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="怎么用" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="词语表" sheetId="1" r:id="rId1"/>
+    <sheet name="怎么用" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+  <si>
+    <t>词语</t>
+  </si>
+  <si>
+    <t>释义</t>
+  </si>
+  <si>
+    <t>把「词语表」那一页的内容换成你自己单元的词语就好。</t>
+  </si>
+  <si>
+    <t>1. 第一行（词语 / 释义）请不要动。</t>
+  </si>
+  <si>
+    <t>2. 一行一个词语。至少 8 个，越多越好（最少 4 个）。</t>
+  </si>
+  <si>
+    <t>3. 错误选项不用你写，程序会自动从其他词语的释义里抓。</t>
+  </si>
+  <si>
+    <t>4. 存档之后，把这个档案连同游戏资料夹一起上传到 Claude，</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   再把资源页上的提示词贴进去，就会帮你改好。</t>
+  </si>
+  <si>
+    <t>资源页：https://kaixinbuilds.github.io/2026AIinSecCLNLC.html</t>
+  </si>
+  <si>
+    <t>人际</t>
+  </si>
+  <si>
+    <t>人和人之间。</t>
+  </si>
+  <si>
+    <t>坦率</t>
+  </si>
+  <si>
+    <t>坦白直率。</t>
+  </si>
+  <si>
+    <t>隐瞒</t>
+  </si>
+  <si>
+    <t>故意不让别人知道，掩盖真相或事实。</t>
+  </si>
+  <si>
+    <t>粗鲁</t>
+  </si>
+  <si>
+    <t>言行不礼貌、不文雅，表现出缺乏修养或教养。</t>
+  </si>
+  <si>
+    <t>分歧</t>
+  </si>
+  <si>
+    <t>意见、想法或看法上的不一致或不同。</t>
+  </si>
+  <si>
+    <t>磋商</t>
+  </si>
+  <si>
+    <t>反复商量、研究；互相商议</t>
+  </si>
+  <si>
+    <t>融洽</t>
+  </si>
+  <si>
+    <t>彼此感情和睦，没有隔阂。</t>
+  </si>
+  <si>
+    <t>诀窍</t>
+  </si>
+  <si>
+    <t>窍门；高明的方法</t>
+  </si>
+  <si>
+    <t>聆听</t>
+  </si>
+  <si>
+    <t>仔细听取</t>
+  </si>
+  <si>
+    <t>死党</t>
+  </si>
+  <si>
+    <t>指关系非常密切、情谊深厚的朋友，通常形容最好的朋友或伙伴。</t>
+  </si>
+  <si>
+    <t>迥然</t>
+  </si>
+  <si>
+    <t>形容差别非常明显，截然不同的样子。</t>
+  </si>
+  <si>
+    <t>咄咄逼人</t>
+  </si>
+  <si>
+    <t>形容态度强硬、过于逼迫别人，给人很大压力。</t>
+  </si>
+  <si>
+    <t>避讳</t>
+  </si>
+  <si>
+    <t>避开敏感或禁忌的话题。</t>
+  </si>
+  <si>
+    <t>橱窗</t>
+  </si>
+  <si>
+    <t>商店临街展览样品的玻璃窗。</t>
+  </si>
+  <si>
+    <t>狭窄</t>
+  </si>
+  <si>
+    <t>指狭小;宽度小</t>
+  </si>
+  <si>
+    <t>铅笔盒</t>
+  </si>
+  <si>
+    <t>学生学习的文具之一</t>
+  </si>
+  <si>
+    <t>拧</t>
+  </si>
+  <si>
+    <t>用力扭转</t>
+  </si>
+  <si>
+    <t>抿</t>
+  </si>
+  <si>
+    <t>用小刷子蘸水或油抹</t>
+  </si>
+  <si>
+    <t>肺炎</t>
+  </si>
+  <si>
+    <t>肺部的炎症</t>
+  </si>
+  <si>
+    <t>纸屑</t>
+  </si>
+  <si>
+    <t>指较为细小的纸碎屑，多为在使用纸制品时留下的碎屑</t>
+  </si>
+  <si>
+    <t>肿瘤</t>
+  </si>
+  <si>
+    <t>当实体组织（如：器官、肌肉或骨骼）里出现癌细胞增长</t>
+  </si>
+  <si>
+    <t>癌症</t>
+  </si>
+  <si>
+    <t>细胞异常增殖失控的疾病</t>
+  </si>
+  <si>
+    <t>擦拭</t>
+  </si>
+  <si>
+    <t>擦抹</t>
+  </si>
+  <si>
+    <t>三缄其口</t>
+  </si>
+  <si>
+    <t>形容说话极其谨慎个，不轻易开口</t>
+  </si>
+  <si>
+    <t>某</t>
+  </si>
+  <si>
+    <t>指不知道名称或不便明说的特定的人或事物</t>
+  </si>
+  <si>
+    <t>苍白</t>
+  </si>
+  <si>
+    <t>白而微青的颜色；形容缺乏生力活力</t>
+  </si>
+  <si>
+    <t>哼</t>
+  </si>
+  <si>
+    <t>表示不满、鄙视或愤恨；表示威胁</t>
+  </si>
+  <si>
+    <t>鼓掌</t>
+  </si>
+  <si>
+    <t>双手击打掌心，表示钦佩或尊重</t>
+  </si>
+  <si>
+    <t>忠实</t>
+  </si>
+  <si>
+    <t>忠诚老实</t>
+  </si>
+  <si>
+    <t>痊愈</t>
+  </si>
+  <si>
+    <t>指疾病或创伤完全康复，恢复健康。</t>
+  </si>
+  <si>
+    <t>清晰</t>
+  </si>
+  <si>
+    <t>指看、说得很清楚</t>
+  </si>
+  <si>
+    <t>调剂</t>
+  </si>
+  <si>
+    <t>调整有无、余缺等情况；调整使合宜。</t>
+  </si>
+  <si>
+    <t>牢骚</t>
+  </si>
+  <si>
+    <t>指抑郁不满的情绪或言语，说说抱怨、不满的话。</t>
+  </si>
+  <si>
+    <t>鄙夷</t>
+  </si>
+  <si>
+    <t>轻视</t>
+  </si>
+  <si>
+    <t>流淌</t>
+  </si>
+  <si>
+    <t>液体流动</t>
+  </si>
+  <si>
+    <t>窗帘</t>
+  </si>
+  <si>
+    <t>遮挡窗户的帘子。多用纺织品、编织品制成。</t>
+  </si>
+  <si>
+    <t>提心吊胆</t>
+  </si>
+  <si>
+    <t>形容担心害怕，安不下心。</t>
+  </si>
+  <si>
+    <t>古董</t>
+  </si>
+  <si>
+    <t>为人所珍视的古代器物</t>
+  </si>
+  <si>
+    <t>轿子</t>
+  </si>
+  <si>
+    <t>旧时的交通工具。方形，用竹子或木头制成，外面套着帷子，两边各有一根杆子，由人抬着走或由骡马驭着走。</t>
+  </si>
+  <si>
+    <t>耻笑</t>
+  </si>
+  <si>
+    <t>轻视和讥笑。</t>
+  </si>
+  <si>
+    <t>搀扶</t>
+  </si>
+  <si>
+    <t>用手扶着别人的胳膊或手</t>
+  </si>
+  <si>
+    <t>罢了</t>
+  </si>
+  <si>
+    <t>表示“仅此而已”的意思</t>
+  </si>
+  <si>
+    <t>姊妹</t>
+  </si>
+  <si>
+    <t>姐姐和妹妹</t>
+  </si>
+  <si>
+    <t>无奈</t>
+  </si>
+  <si>
+    <t>无可奈何；没有办法</t>
+  </si>
+  <si>
+    <t>溺爱</t>
+  </si>
+  <si>
+    <t>（对孩子）过分地宠爱。</t>
+  </si>
+  <si>
+    <t>顽劣</t>
+  </si>
+  <si>
+    <t>顽固恶劣，专做坏事的人</t>
+  </si>
+  <si>
+    <t>颈项</t>
+  </si>
+  <si>
+    <t>脖子</t>
+  </si>
+  <si>
+    <t>鬓</t>
+  </si>
+  <si>
+    <t>脸两侧靠近耳朵的头发</t>
+  </si>
+  <si>
+    <t>裁</t>
+  </si>
+  <si>
+    <t>种植；移植幼苗或扦插枝条。</t>
+  </si>
+  <si>
+    <t>桃</t>
+  </si>
+  <si>
+    <t>桃树的果子</t>
+  </si>
+  <si>
+    <t>瓣</t>
+  </si>
+  <si>
+    <t>植物的花冠、种子、果实或鳞茎上可以分开的小片或小块</t>
+  </si>
+  <si>
+    <t>和睦</t>
+  </si>
+  <si>
+    <t>相处融洽友好</t>
+  </si>
+  <si>
+    <t>稀罕</t>
+  </si>
+  <si>
+    <t>少见而不同于一般的</t>
+  </si>
+  <si>
+    <t>改过自新</t>
+  </si>
+  <si>
+    <t>改正错误，重新做人。</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0096521F"/>
+        <fgColor rgb="FF96521F"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,87 +437,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -428,124 +746,452 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>词语</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>释义</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>维护</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>保持、保障，使不受破坏</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>策略</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>为了达到某个目标而定下的计划或方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>催促</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>叫人赶快行动，不要拖延</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>沉浸</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>完全进入某种境界或思想活动中</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>渲染</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>夸大地形容，使气氛更浓</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>斟酌</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>反复考虑，仔细掂量是否合适</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>潜移默化</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>在不知不觉中受到影响而发生变化</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>锲而不舍</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>一直刻下去不放手，比喻有恒心、不放弃</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>105</v>
+      </c>
+      <c r="B51" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>111</v>
+      </c>
+      <c r="B54" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -554,70 +1200,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>把「词语表」那一页的内容换成你自己单元的词语就好。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1. 第一行（词语 / 释义）请不要动。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2. 一行一个词语。至少 8 个，越多越好（最少 4 个）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3. 错误选项不用你写，程序会自动从其他词语的释义里抓。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4. 存档之后，把这个档案连同游戏资料夹一起上传到 Claude，</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   再把资源页上的提示词贴进去，就会帮你改好。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>资源页：https://kaixinbuilds.github.io/2026AIinSecCLNLC.html</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
